--- a/doctool/test/auto/scenario07/システム機能設計書_サンプル_S07_expected.xlsx
+++ b/doctool/test/auto/scenario07/システム機能設計書_サンプル_S07_expected.xlsx
@@ -5,40 +5,39 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tie303229\AppData\Local\Temp\pytest-of-tie303229\pytest-21\scenario07_0\scenario07\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tie303229\AppData\Local\Temp\pytest-of-tie303229\pytest-28\scenario06_0\scenario06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAF5FC8-B214-44F4-B44A-0908018B5467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C3D09B-F80F-4118-BB18-B845728EF3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="エラーシート" sheetId="10" r:id="rId1"/>
-    <sheet name="レビュー結果1回目" sheetId="9" r:id="rId2"/>
-    <sheet name="表紙" sheetId="1" r:id="rId3"/>
-    <sheet name="変更履歴" sheetId="2" r:id="rId4"/>
-    <sheet name="目次" sheetId="3" r:id="rId5"/>
-    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId6"/>
-    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId7"/>
-    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId8"/>
-    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId9"/>
-    <sheet name="データ" sheetId="8" state="hidden" r:id="rId10"/>
+    <sheet name="レビュー結果1回目" sheetId="10" r:id="rId1"/>
+    <sheet name="表紙" sheetId="1" r:id="rId2"/>
+    <sheet name="変更履歴" sheetId="2" r:id="rId3"/>
+    <sheet name="目次" sheetId="3" r:id="rId4"/>
+    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId5"/>
+    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId6"/>
+    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId7"/>
+    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId8"/>
+    <sheet name="データ" sheetId="8" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc46209822" localSheetId="5">'1.  画面取引定義'!$B$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'1.  画面取引定義'!$A$1:$AI$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">データ!$A$1:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー結果1回目!$A$1:$K$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">目次!$A$1:$AI$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'1.  画面取引定義'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
+    <definedName name="_Toc46209822" localSheetId="4">'1.  画面取引定義'!$B$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'1.  画面取引定義'!$A$1:$AI$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">データ!$A$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$K$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">表紙!$A$1:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">目次!$A$1:$AI$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'1.  画面取引定義'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
     <definedName name="引継項目格納先">データ!$B$2:$B$2</definedName>
     <definedName name="画面項目種類">データ!$A$2:$A$14</definedName>
     <definedName name="種別一覧">データ!$C$2:$C$7</definedName>
@@ -77,7 +76,9 @@
           </rPr>
           <t>山田　太郎:*
 実施日:2023/08/01
-開始:09:00</t>
+開始:09:00
+終了:14:00
+レビュー時間:200</t>
         </r>
       </text>
     </comment>
@@ -150,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="319">
   <si>
     <t>第１．２版</t>
   </si>
@@ -1216,24 +1217,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S07</t>
-  </si>
-  <si>
-    <t>＜エラー＞</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>エラー内容</t>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>レビュー日時コメントが正しく入力されていません｡実施日、開始時刻、終了時刻、レビュー時間を全て入力してください。</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$A$4</t>
+    <t>システム機能設計書_サンプル_S06</t>
   </si>
   <si>
     <t>B5</t>
@@ -1999,7 +1983,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2754,10 +2738,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" quotePrefix="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -3199,190 +3179,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CD7F1D-A270-465A-91CB-F66F97D324EC}">
-  <sheetPr codeName="ErrorSheetTemplate">
-    <tabColor theme="3" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="105.1640625" style="287" customWidth="1"/>
-    <col min="2" max="2" width="42.1640625" style="262" customWidth="1"/>
-    <col min="3" max="16384" width="9.33203125" style="262"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="286" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="287" t="s">
-        <v>308</v>
-      </c>
-      <c r="B2" s="262" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="27" x14ac:dyDescent="0.15">
-      <c r="A3" s="287" t="s">
-        <v>309</v>
-      </c>
-      <c r="B3" s="298" t="s">
-        <v>310</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <hyperlinks>
-    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$A$4" display="'2. WA1020101(プロジェクト登録画面)'!$A$4" xr:uid="{C48C95AC-09D6-470C-98CC-D271F69283F6}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Sheet6">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" s="52" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="52" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78311821-9CB0-4082-966B-86E6FFFA60CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF062FD-EA7C-4128-A954-D4B0471D90E8}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3449,13 +3246,21 @@
       <c r="C4" s="272">
         <v>1</v>
       </c>
-      <c r="E4" s="273"/>
-      <c r="F4" s="274"/>
+      <c r="E4" s="273">
+        <v>45139</v>
+      </c>
+      <c r="F4" s="274">
+        <v>0.375</v>
+      </c>
       <c r="G4" s="275" t="s">
         <v>275</v>
       </c>
-      <c r="H4" s="274"/>
-      <c r="I4" s="272"/>
+      <c r="H4" s="274">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I4" s="272">
+        <v>200</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A6" s="261" t="s">
@@ -3778,16 +3583,16 @@
         <v>38</v>
       </c>
       <c r="B15" s="297" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C15" s="272" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D15" s="272" t="s">
-        <v>313</v>
-      </c>
-      <c r="E15" s="299" t="s">
-        <v>314</v>
+        <v>309</v>
+      </c>
+      <c r="E15" s="298" t="s">
+        <v>310</v>
       </c>
       <c r="F15" s="271"/>
       <c r="G15" s="271"/>
@@ -3795,7 +3600,7 @@
       <c r="I15" s="271"/>
       <c r="J15" s="271"/>
       <c r="K15" s="272" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L15" s="295">
         <f t="shared" ref="L15:T18" si="1">IF($D15=L$14,1,0)</f>
@@ -3845,16 +3650,16 @@
         <v>38</v>
       </c>
       <c r="B16" s="297" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C16" s="272" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D16" s="272" t="s">
-        <v>317</v>
-      </c>
-      <c r="E16" s="299" t="s">
-        <v>318</v>
+        <v>313</v>
+      </c>
+      <c r="E16" s="298" t="s">
+        <v>314</v>
       </c>
       <c r="F16" s="271"/>
       <c r="G16" s="271"/>
@@ -3862,7 +3667,7 @@
       <c r="I16" s="271"/>
       <c r="J16" s="271"/>
       <c r="K16" s="272" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L16" s="295">
         <f t="shared" si="1"/>
@@ -3912,16 +3717,16 @@
         <v>38</v>
       </c>
       <c r="B17" s="297" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C17" s="272" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D17" s="272" t="s">
-        <v>320</v>
-      </c>
-      <c r="E17" s="299" t="s">
-        <v>321</v>
+        <v>316</v>
+      </c>
+      <c r="E17" s="298" t="s">
+        <v>317</v>
       </c>
       <c r="F17" s="271"/>
       <c r="G17" s="271"/>
@@ -3929,7 +3734,7 @@
       <c r="I17" s="271"/>
       <c r="J17" s="271"/>
       <c r="K17" s="272" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L17" s="295">
         <f t="shared" si="1"/>
@@ -4045,14 +3850,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{96627C1A-8A77-495C-A97D-AAD7A5447C63}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{F098D135-98D2-4CF9-9B4E-8148AAF06094}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{8B0C9474-1BDC-4E65-8B88-1407678B2A65}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{ABA52771-81D0-470E-809D-AA4C41203AA9}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{F6356A96-41D2-4007-89BC-9373A0D4320B}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{2D934BCE-676E-4AB6-8EA1-51EB48566C1B}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{C386EDB7-5294-4877-9398-D00BCFF012D5}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{5CAA2169-1EF7-48F5-967E-34A86387CE6F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
@@ -4060,7 +3865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
@@ -4740,7 +4545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
@@ -6301,7 +6106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
@@ -7047,7 +6852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
@@ -7553,7 +7358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
@@ -11854,7 +11659,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
@@ -15373,7 +15178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
@@ -16543,4 +16348,143 @@
     <brk id="33" max="34" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet6">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="52" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="52" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>